--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484631_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484631_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9361</v>
+        <v>7.8474</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5526</v>
+        <v>5.9345</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3836</v>
+        <v>1.9129</v>
       </c>
       <c r="G2" t="n">
         <v>5.9679</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6854</v>
+        <v>0.5967</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2074</v>
+        <v>0.5894</v>
       </c>
       <c r="U2" t="n">
-        <v>0.478</v>
+        <v>0.0073</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>6.1587</v>
       </c>
       <c r="E3" t="n">
-        <v>3.772</v>
+        <v>3.4013</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2281</v>
+        <v>2.7574</v>
       </c>
       <c r="G3" t="n">
         <v>2.5788</v>
@@ -688,13 +688,13 @@
         <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3559</v>
+        <v>0.5145</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3462</v>
+        <v>-0.0245</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0097</v>
+        <v>0.539</v>
       </c>
       <c r="V3" t="n">
         <v>1.5993</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9137</v>
+        <v>2.6601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4117</v>
+        <v>0.2365</v>
       </c>
       <c r="F4" t="n">
-        <v>1.502</v>
+        <v>2.4236</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5219</v>
+        <v>1.1608</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8808</v>
+        <v>1.8151</v>
       </c>
       <c r="I4" t="n">
-        <v>0.641</v>
+        <v>-0.6544</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9744</v>
+        <v>1.108</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5635</v>
+        <v>1.0246</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4109</v>
+        <v>0.0833</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4525</v>
+        <v>0.0528</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3173</v>
+        <v>0.7905</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7698</v>
+        <v>-0.7377</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1991</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.5814</v>
+        <v>-2.7489</v>
       </c>
       <c r="R4" t="n">
         <v>2.3823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0426</v>
+        <v>-0.3565</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.345</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5276</v>
+        <v>-0.0115</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6335</v>
+        <v>2.2224</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5889</v>
+        <v>2.2224</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.549</v>
+        <v>1.8198</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3544</v>
+        <v>0.7141</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9034</v>
+        <v>1.1056</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1608</v>
+        <v>3.5219</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8151</v>
+        <v>2.8808</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6544</v>
+        <v>0.641</v>
       </c>
       <c r="J5" t="n">
-        <v>1.108</v>
+        <v>3.9744</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0246</v>
+        <v>2.5635</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0833</v>
+        <v>1.4109</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0528</v>
+        <v>-0.4525</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7905</v>
+        <v>0.3173</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7377</v>
+        <v>-0.7698</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3665</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>-4.5814</v>
       </c>
       <c r="R5" t="n">
         <v>2.3823</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4676</v>
+        <v>-0.1365</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9359</v>
+        <v>-0.2677</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5318000000000001</v>
+        <v>0.1312</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2224</v>
+        <v>0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2224</v>
+        <v>1.5889</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.548</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3054</v>
+        <v>-0.003</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0307</v>
+        <v>1.551</v>
       </c>
       <c r="G6" t="n">
         <v>3.2481</v>
@@ -922,13 +922,13 @@
         <v>2.9321</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.761</v>
+        <v>-0.9384</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.46</v>
+        <v>-0.1576</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.301</v>
+        <v>-0.7808</v>
       </c>
       <c r="V6" t="n">
         <v>-0.945</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4265</v>
+        <v>0.5366</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0442</v>
+        <v>0.1543</v>
       </c>
       <c r="F7" t="n">
         <v>0.3823</v>
@@ -1000,10 +1000,10 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1833</v>
+        <v>-0.0732</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3303</v>
+        <v>-0.2202</v>
       </c>
       <c r="U7" t="n">
         <v>0.1471</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2238</v>
+        <v>-0.0315</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8563</v>
+        <v>-0.664</v>
       </c>
       <c r="F8" t="n">
         <v>0.6326000000000001</v>
@@ -1078,10 +1078,10 @@
         <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1011</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1101</v>
+        <v>0.0822</v>
       </c>
       <c r="U8" t="n">
         <v>0.0188</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3189</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4225</v>
+        <v>-2.9444</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1037</v>
+        <v>2.1284</v>
       </c>
       <c r="G9" t="n">
         <v>0.8004</v>
@@ -1156,13 +1156,13 @@
         <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7133</v>
+        <v>0.2162</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6214</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0919</v>
+        <v>0.1167</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3794</v>
+        <v>-1.0577</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8739</v>
+        <v>-0.6266</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5054</v>
+        <v>-0.4311</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0519</v>
@@ -1234,13 +1234,13 @@
         <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.105</v>
+        <v>-0.7834</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3854</v>
+        <v>-0.138</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7197</v>
+        <v>-0.6454</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3219</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8666</v>
+        <v>-2.0776</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8385</v>
+        <v>-3.2476</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9718</v>
+        <v>1.17</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6218</v>
@@ -1312,13 +1312,13 @@
         <v>2.7489</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.389</v>
+        <v>-0.5999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.1798</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6183</v>
+        <v>-0.4201</v>
       </c>
       <c r="V11" t="n">
         <v>0.3115</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.7619</v>
+        <v>16.5878</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1295</v>
+        <v>2.955099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>13.6328</v>
+        <v>13.6327</v>
       </c>
       <c r="G12" t="n">
         <v>12.393</v>
@@ -1390,13 +1390,13 @@
         <v>18.3256</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2852</v>
+        <v>-1.4594</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3875</v>
+        <v>-0.5616</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.8976999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>3.8217</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1492</v>
+        <v>5.7816</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8381</v>
+        <v>4.2227</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3111</v>
+        <v>1.5589</v>
       </c>
       <c r="G13" t="n">
         <v>4.7834</v>
@@ -1468,13 +1468,13 @@
         <v>3.1154</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3122</v>
+        <v>0.3201</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2956</v>
+        <v>0.089</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0166</v>
+        <v>0.2311</v>
       </c>
       <c r="V13" t="n">
         <v>0.3115</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9519</v>
+        <v>0.4581</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2508</v>
+        <v>0.3854</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2989</v>
+        <v>0.0727</v>
       </c>
       <c r="G16" t="n">
         <v>-1.6835</v>
@@ -1702,13 +1702,13 @@
         <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0698</v>
+        <v>0.576</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3892</v>
+        <v>0.5238</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3194</v>
+        <v>0.0522</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6335</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8565</v>
+        <v>-1.48</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1155</v>
+        <v>-2.7885</v>
       </c>
       <c r="F18" t="n">
-        <v>1.259</v>
+        <v>1.3085</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1528</v>
@@ -1858,13 +1858,13 @@
         <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9297</v>
+        <v>0.3062</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4925</v>
+        <v>-0.1806</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4372</v>
+        <v>0.4868</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6496</v>
+        <v>-1.6643</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4952</v>
+        <v>-2.0144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8456</v>
+        <v>0.3502</v>
       </c>
       <c r="G19" t="n">
         <v>0.9205</v>
@@ -1936,13 +1936,13 @@
         <v>2.1991</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1184</v>
+        <v>1.1037</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3506</v>
+        <v>0.1301</v>
       </c>
       <c r="U19" t="n">
-        <v>1.469</v>
+        <v>0.9736</v>
       </c>
       <c r="V19" t="n">
         <v>-2.2224</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2155</v>
+        <v>-2.4355</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0279</v>
+        <v>-2.124</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1876</v>
+        <v>-0.3114</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8659</v>
@@ -2014,13 +2014,13 @@
         <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.3026</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0196</v>
+        <v>-0.1157</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.063</v>
+        <v>-0.1869</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7461</v>
+        <v>-3.6966</v>
       </c>
       <c r="E21" t="n">
         <v>-3.1955</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5506</v>
+        <v>-0.5011</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6714</v>
@@ -2092,13 +2092,13 @@
         <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3626</v>
+        <v>0.4121</v>
       </c>
       <c r="T21" t="n">
         <v>0.5121</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1495</v>
+        <v>-0.0999</v>
       </c>
       <c r="V21" t="n">
         <v>0.3115</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.804</v>
+        <v>-4.922</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0223</v>
+        <v>-3.2146</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7817</v>
+        <v>-1.7074</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7058</v>
@@ -2170,13 +2170,13 @@
         <v>2.9321</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6561</v>
+        <v>0.4638</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1619</v>
+        <v>0.2362</v>
       </c>
       <c r="V22" t="n">
         <v>-1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4037</v>
+        <v>-5.0686</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2024</v>
+        <v>-2.8178</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2013</v>
+        <v>-2.2508</v>
       </c>
       <c r="G23" t="n">
         <v>-4.6633</v>
@@ -2248,13 +2248,13 @@
         <v>0.3665</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7849</v>
+        <v>-0.4498</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.3861</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0142</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0135</v>
+        <v>-5.5604</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4885</v>
+        <v>-4.9115</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.525</v>
+        <v>-0.6489</v>
       </c>
       <c r="G24" t="n">
         <v>-5.1797</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8337</v>
+        <v>-0.3807</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7157</v>
+        <v>-0.1387</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.118</v>
+        <v>-0.2419</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.7623</v>
+        <v>-15.7622</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.6329</v>
+        <v>-13.6327</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1294</v>
+        <v>-2.1293</v>
       </c>
       <c r="G25" t="n">
         <v>-12.393</v>
@@ -2404,13 +2404,13 @@
         <v>16.4932</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2851</v>
+        <v>2.285</v>
       </c>
       <c r="T25" t="n">
         <v>0.8976999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3874</v>
+        <v>1.3875</v>
       </c>
       <c r="V25" t="n">
         <v>-3.8218</v>
